--- a/testprocess/0-templet/project-info.xlsx
+++ b/testprocess/0-templet/project-info.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>项目来源</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -38,83 +38,104 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>网络资源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此处填写应用项目的网络资源，例如带宽、子网划分等等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目简介</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应用流程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此处详细介绍应用项目的具体流程。例如数据处理过程、数据访问流程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此处介绍项目背景、来源、用途等等信息。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目规模</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此处填写应用数据规模（TB、PB），集群规模（节点数目），需要处理的访问请求数目等等。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特点和难点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>典型应用场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hadoop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否共同部署hadoop及其它软件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此处填写在项目实施过程中有关SequoiaDB特殊功能点和瓶颈点。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实例说明典型应用场景。可以结合典型应用场景具体介绍该项目重点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动接口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应用程序采用的驱动接口。如果有对方的应用程序更好，或者是关键程序片段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可靠性要求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备份要求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据的备份规划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此处可以模拟实际项目过程中常见的故障类型，例如网络不通，网络不稳定，机柜掉电，机器硬盘故障等等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>此处填写代表性的机器配置。例如CPU、内存、硬盘型号。一台机器挂载多少个硬盘。是否使用磁盘阵列、SSD硬盘。是否用到了其它加快IO的设备</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>网络资源</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此处填写应用项目的网络资源，例如带宽、子网划分等等</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>项目简介</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>应用流程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此处详细介绍应用项目的具体流程。例如数据处理过程、数据访问流程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此处介绍项目背景、来源、用途等等信息。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>项目规模</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此处填写应用数据规模（TB、PB），集群规模（节点数目），需要处理的访问请求数目等等。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特点和难点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>典型应用场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hadoop</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否共同部署hadoop及其它软件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此处填写在项目实施过程中有关SequoiaDB特殊功能点和瓶颈点。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实例说明典型应用场景。可以结合典型应用场景具体介绍该项目重点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>驱动接口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>应用程序采用的驱动接口。如果有对方的应用程序更好，或者是关键程序片段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可靠性要求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备份要求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据的备份规划</t>
+    <t>数据格式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据分布</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>示例说明实际应用数据记录，例如记录长度、字段数、每个字段类型、取值范围、是否可为NULL、字段不存在等等属性。
+如果是字符串类型，那么该字段长度范围，是否包含中文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据分布方案（分区键、分区方式、主子表）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -573,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="21.625" style="3" customWidth="1"/>
@@ -590,26 +611,26 @@
     </row>
     <row r="2" spans="1:2" ht="23.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="24.75" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="25.5" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.75" customHeight="1">
@@ -625,60 +646,79 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="22.5" customHeight="1">
       <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="20.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="24" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="22.5" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="21" customHeight="1">
       <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="20.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="23.25" customHeight="1">
       <c r="A13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>24</v>
+    </row>
+    <row r="14" spans="1:2" ht="30.75" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="20.25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/testprocess/0-templet/project-info.xlsx
+++ b/testprocess/0-templet/project-info.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>项目来源</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,18 +34,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>硬件资源</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>网络资源</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>此处填写应用项目的网络资源，例如带宽、子网划分等等</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>项目简介</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -66,10 +58,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>此处填写应用数据规模（TB、PB），集群规模（节点数目），需要处理的访问请求数目等等。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>特点和难点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -86,39 +74,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>此处填写在项目实施过程中有关SequoiaDB特殊功能点和瓶颈点。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>实例说明典型应用场景。可以结合典型应用场景具体介绍该项目重点</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>驱动接口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>应用程序采用的驱动接口。如果有对方的应用程序更好，或者是关键程序片段</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>可靠性要求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>备份要求</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>数据的备份规划</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此处可以模拟实际项目过程中常见的故障类型，例如网络不通，网络不稳定，机柜掉电，机器硬盘故障等等</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>此处填写代表性的机器配置。例如CPU、内存、硬盘型号。一台机器挂载多少个硬盘。是否使用磁盘阵列、SSD硬盘。是否用到了其它加快IO的设备</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -136,6 +100,50 @@
   </si>
   <si>
     <t>数据分布方案（分区键、分区方式、主子表）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此处填写应用数据规模（TB、PB），集群规模（节点数目），需要处理的访问请求数目等等。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此处填写代表性的机器配置。例如CPU、内存、硬盘型号。一台机器挂载多少个硬盘。是否使用磁盘阵列、SSD硬盘。是否用到了其它加快IO的设备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硬件资源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>软件资源</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>操作系统、第三方工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此处填写应用项目的网络资源，例如带宽、子网划分等等。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此处填写在项目实施过程中有关SequoiaDB特殊功能点和瓶颈点。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可靠性要求</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>此处可以模拟实际项目过程中常见的故障类型，例如网络不通，网络不稳定，机柜掉电，机器硬盘故障等等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据的备份规划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>驱动接口</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -143,7 +151,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,6 +179,15 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -218,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -231,6 +248,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -594,10 +614,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="21.625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="18.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="132.875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
@@ -611,26 +631,26 @@
     </row>
     <row r="2" spans="1:2" ht="23.25" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="24.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="25.5" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="24.75" customHeight="1">
@@ -643,84 +663,93 @@
     </row>
     <row r="6" spans="1:2" ht="20.25" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="20.25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="B8" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="20.25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="24" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="4" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="21" customHeight="1">
+      <c r="A12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="20.25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="23.25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="26.25" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="24" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="B15" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="20.25" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="22.5" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="21" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="23.25" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="30.75" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="20.25" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
+    <row r="17" ht="21" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
